--- a/order_forms/044_crawfish_preorder_form--order_forms.xlsx
+++ b/order_forms/044_crawfish_preorder_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'crawfish',_'value':_'crawfish'}</t>
+          <t>crawfish</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Crawfish', 'value': 'crawfish'}</t>
+          <t>Crawfish</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'shrimp',_'value':_'shrimp'}</t>
+          <t>shrimp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Shrimp', 'value': 'shrimp'}</t>
+          <t>Shrimp</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'available',_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Available', 'value': 'available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'out_of_stock',_'value':_'out_of_stock'}</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Out of Stock', 'value': 'out_of_stock'}</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'available',_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Available', 'value': 'available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'out_of_stock',_'value':_'out_of_stock'}</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Out of Stock', 'value': 'out_of_stock'}</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'available',_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Available', 'value': 'available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'no_response',_'value':_'no_response'}</t>
+          <t>no_response</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'No Response', 'value': 'no_response'}</t>
+          <t>No Response</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Rejected', 'value': 'rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
